--- a/assembly_5/BOM_JLCSMT.xlsx
+++ b/assembly_5/BOM_JLCSMT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\warcgr01\WORKSPACE\moto_logic_board\assembly_5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A365E5AB-D236-41BA-992C-A51B3F79855C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6FC3C7-E0A5-4D48-9191-0D1057DC6EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>Comment</t>
   </si>
@@ -324,10 +324,14 @@
     <t>200K</t>
   </si>
   <si>
-    <t>C1671</t>
-  </si>
-  <si>
     <t>R26,R2,R28,R4,R29,R24,R19,R17,R22,R25,R27</t>
+  </si>
+  <si>
+    <t>C14857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+C1525</t>
   </si>
 </sst>
 </file>
@@ -420,7 +424,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -443,6 +447,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -819,8 +826,8 @@
         <v>5</v>
       </c>
       <c r="C2" s="5"/>
-      <c r="D2" s="7" t="s">
-        <v>46</v>
+      <c r="D2" s="10" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
@@ -874,7 +881,7 @@
         <v>71</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="8" t="s">
@@ -1192,7 +1199,7 @@
         <v>39</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="20.100000000000001" customHeight="1">
